--- a/테스트/테스트3차/5회/박도겸/테스트시나리오_박도겸.xlsx
+++ b/테스트/테스트3차/5회/박도겸/테스트시나리오_박도겸.xlsx
@@ -432,7 +432,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1780,7 +1780,7 @@
 전화번호2: (없음)
 Email: test-pdk@example.com / Fax: 02-0000-0000
 주소: 04524 서울특별시 중구 세종대로 110 / 테스트용 주소(3차 5회 박도겸)
-송금자명: 박도겸 / 현금영수증: 소득공제·강정석·010-8765-3684
+송금자명: 박도겸 / 현금영수증: 소득공제·010-8765-3684
 건보등록: 신규 등록 완료 · 2026-09-07</t>
         </is>
       </c>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="B2" s="52" t="inlineStr">
         <is>
-          <t>TC-006</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="C2" s="53" t="inlineStr">
@@ -3865,27 +3865,27 @@
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>처방전의 병원명과 저장된 병원명이 다름 — 요양기관번호가 이미 다른 병원의 것</t>
+          <t>5회 테스트 자료의 가상 병원 8곳이 병원 마스터에 미등록</t>
         </is>
       </c>
       <c r="F2" s="15" t="inlineStr">
         <is>
-          <t>새 병원 등록에 「대한새봄대학교병원 / 37100017」 입력 후 [등록하고 고르기]</t>
+          <t>병원 조회에서 「대한새봄」 검색</t>
         </is>
       </c>
       <c r="G2" s="15" t="inlineStr">
         <is>
-          <t>새 병원이 등록된다</t>
+          <t>조회 결과 표시</t>
         </is>
       </c>
       <c r="H2" s="15" t="inlineStr">
         <is>
-          <t>「이미 같은 요양기관번호를 쓰는 병원이 있습니다」로 차단됨. 37100017 은 마스터의 경북대학교병원 번호</t>
+          <t>조회 결과 0건</t>
         </is>
       </c>
       <c r="I2" s="15" t="inlineStr">
         <is>
-          <t>중복 차단은 정상 동작(번호가 겹치면 청구가 남의 병원으로 간다). 번호의 임자인 경북대학교병원을 선택하여 진행. 시험 자료가 실재 요양기관번호를 사용한 탓 — 다음 회차 자료는 미사용 번호로 만들 것</t>
+          <t>화면의 [새 병원 등록]으로 등록 후 진행 (TC-006). 시스템 결함 아님 — 8명 모두 동일 절차 필요</t>
         </is>
       </c>
       <c r="J2" s="52" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="B3" s="55" t="inlineStr">
         <is>
-          <t>TC-015</t>
+          <t>TC-006</t>
         </is>
       </c>
       <c r="C3" s="56" t="inlineStr">
@@ -3927,32 +3927,32 @@
       </c>
       <c r="D3" s="55" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>본인부담금 0원 건은 결제 안내 SMS가 발송되지 않음</t>
+          <t>처방전의 병원명과 저장된 병원명이 다름 — 요양기관번호가 이미 다른 병원의 것</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>차상위경감(0/100) 건에서 [주문 생성 및 연계]</t>
+          <t>새 병원 등록에 「대한새봄대학교병원 / 37100017」 입력 후 [등록하고 고르기]</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>접수 안내·결제 안내 2건 발송</t>
+          <t>새 병원이 등록된다</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>접수 안내만 발송 — 「본인부담금이 없어 결제 안내는 보내지 않았습니다」</t>
+          <t>「이미 같은 요양기관번호를 쓰는 병원이 있습니다」로 차단됨. 37100017 은 마스터의 경북대학교병원 번호</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>의도된 동작. 받을 돈이 없으면 결제 안내도 가상계좌도 만들지 않으며, 미발송 사유를 화면에 표시함. 결함 아님</t>
+          <t>중복 차단은 정상 동작(번호가 겹치면 청구가 남의 병원으로 간다). 번호의 임자인 경북대학교병원을 선택하여 진행. 시험 자료가 실재 요양기관번호를 사용한 탓 — 다음 회차 자료는 미사용 번호로 만들 것</t>
         </is>
       </c>
       <c r="J3" s="55" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B4" s="52" t="inlineStr">
         <is>
-          <t>TC-005</t>
+          <t>TC-012</t>
         </is>
       </c>
       <c r="C4" s="53" t="inlineStr">
@@ -3994,32 +3994,32 @@
       </c>
       <c r="D4" s="52" t="inlineStr">
         <is>
-          <t>데이터</t>
+          <t>수행</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>5회 테스트 자료의 가상 병원 8곳이 병원 마스터에 미등록</t>
+          <t>서명 캔버스가 전체화면 캡처 후 초기화됨</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
         <is>
-          <t>병원 조회에서 「대한새봄」 검색</t>
+          <t>서명 입력 → 전체화면(fullPage) 캡처 → 동의 서명 클릭</t>
         </is>
       </c>
       <c r="G4" s="15" t="inlineStr">
         <is>
-          <t>조회 결과 표시</t>
+          <t>서명이 유지된 상태로 제출</t>
         </is>
       </c>
       <c r="H4" s="15" t="inlineStr">
         <is>
-          <t>조회 결과 0건</t>
+          <t>「서명이 비어 있습니다」로 차단</t>
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr">
         <is>
-          <t>화면의 [새 병원 등록]으로 등록 후 진행 (TC-006). 시스템 결함 아님 — 8명 모두 동일 절차 필요</t>
+          <t>서명은 화면에 보이는 상태에서 입력하고, 잉크 유무를 확인한 뒤 제출. 캡처는 제출 전 일반 캡처로 수행</t>
         </is>
       </c>
       <c r="J4" s="52" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="B5" s="55" t="inlineStr">
         <is>
-          <t>TC-012</t>
+          <t>TC-013</t>
         </is>
       </c>
       <c r="C5" s="56" t="inlineStr">
@@ -4061,32 +4061,32 @@
       </c>
       <c r="D5" s="55" t="inlineStr">
         <is>
-          <t>수행</t>
+          <t>환경</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>서명 캔버스가 전체화면 캡처 후 초기화됨</t>
+          <t>동의 완료 시 공단 등록 서류 팩스가 자동 발송되지 않음</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>서명 입력 → 전체화면(fullPage) 캡처 → 동의 서명 클릭</t>
+          <t>위임동의 서명 완료 → 발송 이력 확인</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>서명이 유지된 상태로 제출</t>
+          <t>설정에 따라 자동 발송</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>「서명이 비어 있습니다」로 차단</t>
+          <t>자동 발송되지 않음</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>서명은 화면에 보이는 상태에서 입력하고, 잉크 유무를 확인한 뒤 제출. 캡처는 제출 전 일반 캡처로 수행</t>
+          <t>[동의 완료에 공단 팩스 발송] 설정이 꺼져 있는 상태. 설정값대로 동작한 것이며 결함 아님. TC-013a 수동 발송으로 진행</t>
         </is>
       </c>
       <c r="J5" s="55" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>TC-013</t>
+          <t>TC-015</t>
         </is>
       </c>
       <c r="C6" s="53" t="inlineStr">
@@ -4128,32 +4128,32 @@
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>동의 완료 시 공단 등록 서류 팩스가 자동 발송되지 않음</t>
+          <t>본인부담금 0원 건은 결제 안내 SMS가 발송되지 않음</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
-          <t>위임동의 서명 완료 → 발송 이력 확인</t>
+          <t>차상위경감(0/100) 건에서 [주문 생성 및 연계]</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>설정에 따라 자동 발송</t>
+          <t>접수 안내·결제 안내 2건 발송</t>
         </is>
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>자동 발송되지 않음</t>
+          <t>접수 안내만 발송 — 「본인부담금이 없어 결제 안내는 보내지 않았습니다」</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>[동의 완료에 공단 팩스 발송] 설정이 꺼져 있는 상태. 설정값대로 동작한 것이며 결함 아님. TC-013a 수동 발송으로 진행</t>
+          <t>의도된 동작. 받을 돈이 없으면 결제 안내도 가상계좌도 만들지 않으며, 미발송 사유를 화면에 표시함. 결함 아님</t>
         </is>
       </c>
       <c r="J6" s="52" t="inlineStr">
@@ -4264,7 +4264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>01_처방자료업로드-빈화면.png</t>
+          <t>00_테스트설정.png</t>
         </is>
       </c>
       <c r="C2" s="52" t="inlineStr">
         <is>
-          <t>TC-001</t>
+          <t>사전</t>
         </is>
       </c>
       <c r="D2" s="53" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>처방자료 업로드 초기 화면</t>
+          <t>설정 › 서비스 연동 설정 › 테스트 설정 (_계획 폴더)</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>02_거래처조회-0건.png</t>
+          <t>01_처방자료업로드-빈화면.png</t>
         </is>
       </c>
       <c r="C3" s="55" t="inlineStr">
@@ -4340,14 +4340,14 @@
           <t>TC-001</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>팝업</t>
+      <c r="D3" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>이름 조회 — 찾은 사람 없음(0건)</t>
+          <t>처방자료 업로드 초기 화면</t>
         </is>
       </c>
     </row>
@@ -4357,12 +4357,12 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>03_신규거래처-입력.png</t>
+          <t>02_거래처조회-0건.png</t>
         </is>
       </c>
       <c r="C4" s="52" t="inlineStr">
         <is>
-          <t>TC-002</t>
+          <t>TC-001</t>
         </is>
       </c>
       <c r="D4" s="57" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>이름 조회 팝업 — 이름·주민번호 입력, [신규] 노출</t>
+          <t>이름 조회 — 찾은 사람 없음(0건)</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>04_신규거래처-등록됨.png</t>
+          <t>03_신규거래처-입력.png</t>
         </is>
       </c>
       <c r="C5" s="55" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>거래처 등록 완료 — 생년월일·성별 자동 입력</t>
+          <t>이름 조회 팝업 — 이름·주민번호 입력, [신규] 노출</t>
         </is>
       </c>
     </row>
@@ -4407,22 +4407,22 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>05_서류업로드-17건.png</t>
+          <t>04_신규거래처-등록됨.png</t>
         </is>
       </c>
       <c r="C6" s="52" t="inlineStr">
         <is>
-          <t>TC-003</t>
-        </is>
-      </c>
-      <c r="D6" s="53" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+          <t>TC-002</t>
+        </is>
+      </c>
+      <c r="D6" s="57" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>서류 17건 업로드 (처방전1·신분증1·등록신청서1·결과지14)</t>
+          <t>거래처 등록 완료 — 생년월일·성별 자동 입력</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>06_주문등록-열림.png</t>
+          <t>05_서류업로드-17건.png</t>
         </is>
       </c>
       <c r="C7" s="55" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>RX-20260907-006 주문 등록 화면</t>
+          <t>서류 17건 업로드 (처방전1·신분증1·등록신청서1·결과지14)</t>
         </is>
       </c>
     </row>
@@ -4457,22 +4457,22 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>07_거래처수정-채움.png</t>
+          <t>06_주문등록-열림.png</t>
         </is>
       </c>
       <c r="C8" s="52" t="inlineStr">
         <is>
-          <t>TC-004</t>
-        </is>
-      </c>
-      <c r="D8" s="57" t="inlineStr">
-        <is>
-          <t>팝업</t>
+          <t>TC-003</t>
+        </is>
+      </c>
+      <c r="D8" s="53" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>거래처 수정 — 연락처·주소·결제 방식(가상계좌)</t>
+          <t>RX-20260907-006 주문 등록 화면</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>08_거래처수정-저장.png</t>
+          <t>07_거래처수정-채움.png</t>
         </is>
       </c>
       <c r="C9" s="55" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>거래처 수정 저장 완료</t>
+          <t>거래처 수정 — 연락처·주소·결제 방식(가상계좌)</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>09_상세목록-상담환자정보.png</t>
+          <t>08_거래처수정-저장.png</t>
         </is>
       </c>
       <c r="C10" s="52" t="inlineStr">
@@ -4515,14 +4515,14 @@
           <t>TC-004</t>
         </is>
       </c>
-      <c r="D10" s="53" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D10" s="57" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>상세 목록 › 상담ㆍ환자 정보 — 건보등록 칸</t>
+          <t>거래처 수정 저장 완료</t>
         </is>
       </c>
     </row>
@@ -4532,22 +4532,22 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>10_병원조회-0건.png</t>
+          <t>09_상세목록-상담환자정보.png</t>
         </is>
       </c>
       <c r="C11" s="55" t="inlineStr">
         <is>
-          <t>TC-005</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>팝업</t>
+          <t>TC-004</t>
+        </is>
+      </c>
+      <c r="D11" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>병원 조회 — 「대한새봄」 0건</t>
+          <t>상세 목록 › 상담ㆍ환자 정보 — 건보등록 칸</t>
         </is>
       </c>
     </row>
@@ -4557,12 +4557,12 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>11_새병원등록-채움.png</t>
+          <t>10_병원조회-0건.png</t>
         </is>
       </c>
       <c r="C12" s="52" t="inlineStr">
         <is>
-          <t>TC-006</t>
+          <t>TC-005</t>
         </is>
       </c>
       <c r="D12" s="57" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>새 병원 등록 입력 — 요양기관번호 37100017</t>
+          <t>병원 조회 — 「대한새봄」 0건</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>12_병원채워짐.png</t>
+          <t>11_새병원등록-채움.png</t>
         </is>
       </c>
       <c r="C13" s="55" t="inlineStr">
@@ -4590,14 +4590,14 @@
           <t>TC-006</t>
         </is>
       </c>
-      <c r="D13" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>토스트 「경북대학교병원 - 37100017」</t>
+          <t>새 병원 등록 입력 — 요양기관번호 37100017</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>12a_병원조회-기호로.png</t>
+          <t>12_병원채워짐.png</t>
         </is>
       </c>
       <c r="C14" s="52" t="inlineStr">
@@ -4615,14 +4615,14 @@
           <t>TC-006</t>
         </is>
       </c>
-      <c r="D14" s="57" t="inlineStr">
-        <is>
-          <t>팝업</t>
+      <c r="D14" s="53" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>요양기관번호의 임자를 목록에서 확인</t>
+          <t>토스트 「경북대학교병원 - 37100017」</t>
         </is>
       </c>
     </row>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>13_상세목록-병원처방정보.png</t>
+          <t>12a_병원조회-기호로.png</t>
         </is>
       </c>
       <c r="C15" s="55" t="inlineStr">
         <is>
-          <t>TC-007</t>
-        </is>
-      </c>
-      <c r="D15" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+          <t>TC-006</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>상세 목록 › 병원ㆍ처방 정보 입력 완료</t>
+          <t>요양기관번호의 임자를 목록에서 확인</t>
         </is>
       </c>
     </row>
@@ -4657,22 +4657,22 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>14_청구처찾기.png</t>
+          <t>13_상세목록-병원처방정보.png</t>
         </is>
       </c>
       <c r="C16" s="52" t="inlineStr">
         <is>
-          <t>TC-008</t>
-        </is>
-      </c>
-      <c r="D16" s="57" t="inlineStr">
-        <is>
-          <t>팝업</t>
+          <t>TC-007</t>
+        </is>
+      </c>
+      <c r="D16" s="53" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>관할 청구처 찾기 — 공단 중구지사</t>
+          <t>상세 목록 › 병원ㆍ처방 정보 입력 완료</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>15_상세목록-저장.png</t>
+          <t>14_청구처찾기.png</t>
         </is>
       </c>
       <c r="C17" s="55" t="inlineStr">
@@ -4690,14 +4690,14 @@
           <t>TC-008</t>
         </is>
       </c>
-      <c r="D17" s="56" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>상세 목록 저장 완료</t>
+          <t>관할 청구처 찾기 — 공단 중구지사</t>
         </is>
       </c>
     </row>
@@ -4707,12 +4707,12 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>16_검수요청.png</t>
+          <t>15_상세목록-저장.png</t>
         </is>
       </c>
       <c r="C18" s="52" t="inlineStr">
         <is>
-          <t>TC-009</t>
+          <t>TC-008</t>
         </is>
       </c>
       <c r="D18" s="53" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>검수 요청 완료 — 승인자 알림 발송</t>
+          <t>상세 목록 저장 완료</t>
         </is>
       </c>
     </row>
@@ -4732,22 +4732,22 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>17_검수승인-팝업.png</t>
+          <t>16_검수요청.png</t>
         </is>
       </c>
       <c r="C19" s="55" t="inlineStr">
         <is>
-          <t>TC-010</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>팝업</t>
+          <t>TC-009</t>
+        </is>
+      </c>
+      <c r="D19" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>검수 승인 확인 창</t>
+          <t>검수 요청 완료 — 승인자 알림 발송</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>18_검수완료.png</t>
+          <t>17_검수승인-팝업.png</t>
         </is>
       </c>
       <c r="C20" s="52" t="inlineStr">
@@ -4765,14 +4765,14 @@
           <t>TC-010</t>
         </is>
       </c>
-      <c r="D20" s="53" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D20" s="57" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>검수 완료 상태</t>
+          <t>검수 승인 확인 창</t>
         </is>
       </c>
     </row>
@@ -4782,22 +4782,22 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>19_위임동의-발송창.png</t>
+          <t>18_검수완료.png</t>
         </is>
       </c>
       <c r="C21" s="55" t="inlineStr">
         <is>
-          <t>TC-011</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>팝오버</t>
+          <t>TC-010</t>
+        </is>
+      </c>
+      <c r="D21" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>위임동의 SMS 발송 창 — 수신번호·미리보기</t>
+          <t>검수 완료 상태</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>20_위임동의-발송결과.png</t>
+          <t>19_위임동의-발송창.png</t>
         </is>
       </c>
       <c r="C22" s="52" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>위임동의 발송 결과 — 유효 19:19까지</t>
+          <t>위임동의 SMS 발송 창 — 수신번호·미리보기</t>
         </is>
       </c>
     </row>
@@ -4832,22 +4832,22 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>21_서명화면.png</t>
+          <t>20_위임동의-발송결과.png</t>
         </is>
       </c>
       <c r="C23" s="55" t="inlineStr">
         <is>
-          <t>TC-012</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>공개화면</t>
+          <t>TC-011</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>팝오버</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>위임동의 서명 페이지 (비로그인)</t>
+          <t>위임동의 발송 결과 — 유효 19:19까지</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>22_개인정보동의.png</t>
+          <t>21_서명화면.png</t>
         </is>
       </c>
       <c r="C24" s="52" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>개인정보 수집·이용 동의 선택</t>
+          <t>위임동의 서명 페이지 (비로그인)</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>23_서명함.png</t>
+          <t>22_개인정보동의.png</t>
         </is>
       </c>
       <c r="C25" s="55" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>서명 입력 완료</t>
+          <t>개인정보 수집·이용 동의 선택</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>24_동의완료.png</t>
+          <t>23_서명함.png</t>
         </is>
       </c>
       <c r="C26" s="52" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>동의 완료 화면</t>
+          <t>서명 입력 완료</t>
         </is>
       </c>
     </row>
@@ -4932,22 +4932,22 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>31_팩스발송-창.png</t>
+          <t>24_동의완료.png</t>
         </is>
       </c>
       <c r="C27" s="55" t="inlineStr">
         <is>
-          <t>TC-013a</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>팝오버</t>
+          <t>TC-012</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>공개화면</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>공단 신규/재등록 서류 팩스 — 수신처·전송 서류 17종</t>
+          <t>동의 완료 화면</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>32_팩스발송-결과.png</t>
+          <t>31_팩스발송-창.png</t>
         </is>
       </c>
       <c r="C28" s="52" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>공단 팩스 발송 완료 — 접수번호 026090718522400002</t>
+          <t>공단 신규/재등록 서류 팩스 — 수신처·전송 서류 17종</t>
         </is>
       </c>
     </row>
@@ -4982,22 +4982,22 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>25_제품조회.png</t>
+          <t>32_팩스발송-결과.png</t>
         </is>
       </c>
       <c r="C29" s="55" t="inlineStr">
         <is>
-          <t>TC-014</t>
+          <t>TC-013a</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>팝업</t>
+          <t>팝오버</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>제품 조회 — CH14 Male</t>
+          <t>공단 팩스 발송 완료 — 접수번호 026090718522400002</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>26_주문제품-채움.png</t>
+          <t>25_제품조회.png</t>
         </is>
       </c>
       <c r="C30" s="52" t="inlineStr">
@@ -5015,14 +5015,14 @@
           <t>TC-014</t>
         </is>
       </c>
-      <c r="D30" s="53" t="inlineStr">
-        <is>
-          <t>CE Admin</t>
+      <c r="D30" s="57" t="inlineStr">
+        <is>
+          <t>팝업</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>제품 선택 후 금액 배분 — 기관 810,000 / 본인 0</t>
+          <t>제품 조회 — CH14 Male</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>27_주문제품-저장.png</t>
+          <t>26_주문제품-채움.png</t>
         </is>
       </c>
       <c r="C31" s="55" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>주문 제품 저장 완료</t>
+          <t>제품 선택 후 금액 배분 — 기관 810,000 / 본인 0</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>28_주문생성및연계.png</t>
+          <t>27_주문제품-저장.png</t>
         </is>
       </c>
       <c r="C32" s="52" t="inlineStr">
         <is>
-          <t>TC-015</t>
+          <t>TC-014</t>
         </is>
       </c>
       <c r="D32" s="53" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>주문 연계 완료 — 결제 안내 「발송 안 됨」</t>
+          <t>주문 제품 저장 완료</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>29_정산회계-목록.png</t>
+          <t>28_주문생성및연계.png</t>
         </is>
       </c>
       <c r="C33" s="55" t="inlineStr">
         <is>
-          <t>TC-017</t>
+          <t>TC-015</t>
         </is>
       </c>
       <c r="D33" s="56" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>정산/회계 목록</t>
+          <t>주문 연계 완료 — 결제 안내 「발송 안 됨」</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>30_입금확인-뒤.png</t>
+          <t>29_정산회계-목록.png</t>
         </is>
       </c>
       <c r="C34" s="52" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>주문 확정 후 상태 — 입금액 0 · 세금계산서 발행완료</t>
+          <t>정산/회계 목록</t>
         </is>
       </c>
     </row>
@@ -5132,20 +5132,45 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
+          <t>30_입금확인-뒤.png</t>
+        </is>
+      </c>
+      <c r="C35" s="55" t="inlineStr">
+        <is>
+          <t>TC-017</t>
+        </is>
+      </c>
+      <c r="D35" s="56" t="inlineStr">
+        <is>
+          <t>CE Admin</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>주문 확정 후 상태 — 입금액 0 · 세금계산서 발행완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="52" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
           <t>33_ww_판매주문-확정.png</t>
         </is>
       </c>
-      <c r="C35" s="55" t="inlineStr">
+      <c r="C36" s="52" t="inlineStr">
         <is>
           <t>TC-018</t>
         </is>
       </c>
-      <c r="D35" s="59" t="inlineStr">
+      <c r="D36" s="59" t="inlineStr">
         <is>
           <t>위드웍스</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>판매주문 상세 — 판매상태 확정 (본인부담 0원인데도 확정됨)</t>
         </is>

--- a/테스트/테스트3차/5회/박도겸/테스트시나리오_박도겸.xlsx
+++ b/테스트/테스트3차/5회/박도겸/테스트시나리오_박도겸.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'환경설정'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'테스트시나리오'!$A$2:$S$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'테스트시나리오'!$A$2:$S$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'테스트시나리오'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'결함관리'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'캡처목록'!$1:$1</definedName>
@@ -831,7 +831,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CASE-02   |   End-to-End 통합 테스트   |   TC-001 ~ TC-020</t>
+          <t>CASE-02   |   End-to-End 통합 테스트   |   TC-001 ~ TC-021</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>21건 (TC-001 ~ TC-020, TC-013a 포함)</t>
+          <t>22건 (TC-001 ~ TC-021, TC-013a 포함)</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3537,22 +3537,22 @@
       </c>
       <c r="C33" s="38" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>청구</t>
         </is>
       </c>
       <c r="D33" s="39" t="inlineStr">
         <is>
-          <t>최종 상태 검증</t>
+          <t>지자체 청구 — 등기 발송</t>
         </is>
       </c>
       <c r="E33" s="39" t="inlineStr">
         <is>
-          <t>TC-001 ~ TC-018 완료</t>
+          <t>TC-017 완료 · 청구처 = 지자체(시군구청)인 건만 해당</t>
         </is>
       </c>
       <c r="F33" s="39" t="inlineStr">
         <is>
-          <t>주문ㆍ재구매 › 주문 관리 / Finance</t>
+          <t>청구ㆍ회계 › 청구 관리</t>
         </is>
       </c>
       <c r="G33" s="40" t="n">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="H33" s="39" t="inlineStr">
         <is>
-          <t>주문·창고·증빙 상태를 최종 확인한다</t>
+          <t>해당 건의 청구처ㆍ관할이 바르게 서는지 확인한다</t>
         </is>
       </c>
       <c r="I33" s="39" t="inlineStr">
@@ -3575,16 +3575,14 @@
       </c>
       <c r="K33" s="41" t="inlineStr">
         <is>
-          <t>전 구간 처리 결과 확인</t>
+          <t>청구처는 자격이 정한다 — 기초(의료급여)는 지자체, 일반·차상위경감은 공단이다. 그 아래 줄에 어디로 보내는지(공단은 지사·부서, 지자체는 시군구)가 함께 서야 한다. 서지 않으면 건마다 다시 찾아야 한다.</t>
         </is>
       </c>
       <c r="L33" s="42" t="inlineStr">
         <is>
-          <t>① 처방전 RX-20260907-006 = 검수 완료
-② 주문 EUD202609071843301 = confirmed
-③ 창고 S2609070005 = 확정
-④ 세금계산서 (발행완료) 발행
-⑤ 공단 등록 서류 팩스 발송 완료</t>
+          <t>① 청구처 = 지자체(시군구청)
+② 관할 = 상세 목록에서 지정한 시군구 (예: 서울특별시 중구)
+[공단 건] 청구처 = 건강보험공단 · 관할 = 지사ㆍ부서명</t>
         </is>
       </c>
       <c r="M33" s="43" t="inlineStr">
@@ -3600,81 +3598,209 @@
       <c r="S33" s="28" t="inlineStr"/>
     </row>
     <row r="34" ht="82" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="30" t="n"/>
+      <c r="B34" s="30" t="n"/>
+      <c r="C34" s="30" t="n"/>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="30" t="n"/>
+      <c r="F34" s="30" t="n"/>
+      <c r="G34" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>등기로 부친 것을 적는다</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>발송일: 2026-09-07
+등기번호: (우체국 등기번호)
+발송 영수증: (스캔 파일)
+메모: 보낸 곳·담은 서류</t>
+        </is>
+      </c>
+      <c r="J34" s="15" t="inlineStr">
+        <is>
+          <t>［등기 발송］ → ［저장］</t>
+        </is>
+      </c>
+      <c r="K34" s="45" t="inlineStr">
+        <is>
+          <t>POST /nhis/assist/claim/{order}/local-dispatch — 등기로 부친 자취를 LocalClaimDispatch 에 남긴다. 공단은 사이트에 옮겨 적고 지자체는 등기로 부치므로 단추도 서식도 다르다.
+※ 이 걸음은 지자체 건에만 있다. 공단 건은 [청구] 단추로 사이트 입력을 마친 뒤 「청구함」을 남긴다.</t>
+        </is>
+      </c>
+      <c r="L34" s="46" t="inlineStr">
+        <is>
+          <t>① 청구상태 = 청구 완료 · 청구일시 기록
+② 단추가 [등기 발송] 에서 [등기 영수증] 으로 바뀜
+③ 등기번호·영수증을 다시 꺼내 볼 수 있다</t>
+        </is>
+      </c>
+      <c r="M34" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="34" t="inlineStr"/>
+      <c r="O34" s="35" t="inlineStr"/>
+      <c r="P34" s="35" t="inlineStr"/>
+      <c r="Q34" s="35" t="inlineStr"/>
+      <c r="R34" s="35" t="inlineStr"/>
+      <c r="S34" s="34" t="inlineStr"/>
+    </row>
+    <row r="35" ht="82" customHeight="1">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>TC-020</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>CASE-02 처방전·차상위경감(0/100)·가상계좌</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>검증</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>최종 상태 검증</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>TC-001 ~ TC-019 완료</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>주문ㆍ재구매 › 주문 관리 / Finance</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>주문·창고·증빙 상태를 최종 확인한다</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>(입력 없음)</t>
+        </is>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>목록 조회</t>
+        </is>
+      </c>
+      <c r="K35" s="25" t="inlineStr">
+        <is>
+          <t>전 구간 처리 결과 확인</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="inlineStr">
+        <is>
+          <t>① 처방전 RX-20260907-006 = 검수 완료
+② 주문 EUD202609071843301 = confirmed
+③ 창고 S2609070005 = 확정
+④ 세금계산서 (발행완료) 발행
+⑤ 공단 등록 서류 팩스 발송 완료</t>
+        </is>
+      </c>
+      <c r="M35" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="28" t="inlineStr"/>
+      <c r="O35" s="29" t="inlineStr"/>
+      <c r="P35" s="29" t="inlineStr"/>
+      <c r="Q35" s="29" t="inlineStr"/>
+      <c r="R35" s="29" t="inlineStr"/>
+      <c r="S35" s="28" t="inlineStr"/>
+    </row>
+    <row r="36" ht="82" customHeight="1">
+      <c r="A36" s="36" t="inlineStr">
+        <is>
+          <t>TC-021</t>
+        </is>
+      </c>
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>CASE-02 처방전·차상위경감(0/100)·가상계좌</t>
+        </is>
+      </c>
+      <c r="C36" s="38" t="inlineStr">
+        <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="inlineStr">
         <is>
           <t>목록 항목 검증 (판매현황 연계)</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E36" s="39" t="inlineStr">
         <is>
           <t>TC-015 완료</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr">
+      <c r="F36" s="39" t="inlineStr">
         <is>
           <t>Finance / 주문 관리</t>
         </is>
       </c>
-      <c r="G34" s="24" t="n">
+      <c r="G36" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="23" t="inlineStr">
+      <c r="H36" s="39" t="inlineStr">
         <is>
           <t>Finance 목록에서 위드웍스 판매현황 항목이 표시되는지 확인한다</t>
         </is>
       </c>
-      <c r="I34" s="23" t="inlineStr">
+      <c r="I36" s="39" t="inlineStr">
         <is>
           <t>조회 기간: 2026-09-01 ~ 2026-09-30</t>
         </is>
       </c>
-      <c r="J34" s="23" t="inlineStr">
+      <c r="J36" s="39" t="inlineStr">
         <is>
           <t>［검색］</t>
         </is>
       </c>
-      <c r="K34" s="25" t="inlineStr">
+      <c r="K36" s="41" t="inlineStr">
         <is>
           <t>ceWwCols() — Finance·주문 관리·입금 내역·현금영수증·청구 관리·교환/반품/취소 6개 화면이 동일한 위드웍스 판매현황 항목 순서를 공유한다</t>
         </is>
       </c>
-      <c r="L34" s="26" t="inlineStr">
+      <c r="L36" s="42" t="inlineStr">
         <is>
           <t>① 출고창고·납품창고 항목 표시
 ② 유형·구매 거래처·매출 금액·제품그룹 등 판매현황 항목이 값과 함께 표시
 ③ 구분(SB/SCI)·주민등록번호(마스킹)·상병코드·횟수는 자사 데이터로 표시</t>
         </is>
       </c>
-      <c r="M34" s="27" t="inlineStr">
+      <c r="M36" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N34" s="28" t="inlineStr"/>
-      <c r="O34" s="29" t="inlineStr"/>
-      <c r="P34" s="29" t="inlineStr"/>
-      <c r="Q34" s="29" t="inlineStr"/>
-      <c r="R34" s="29" t="inlineStr"/>
-      <c r="S34" s="28" t="inlineStr"/>
+      <c r="N36" s="28" t="inlineStr"/>
+      <c r="O36" s="29" t="inlineStr"/>
+      <c r="P36" s="29" t="inlineStr"/>
+      <c r="Q36" s="29" t="inlineStr"/>
+      <c r="R36" s="29" t="inlineStr"/>
+      <c r="S36" s="28" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S34"/>
-  <mergeCells count="57">
+  <autoFilter ref="A2:S36"/>
+  <mergeCells count="63">
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="B27:B28"/>
@@ -3682,7 +3808,9 @@
     <mergeCell ref="F25:F26"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C33:C34"/>
     <mergeCell ref="F12:F13"/>
+    <mergeCell ref="E33:E34"/>
     <mergeCell ref="C20:C23"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="A7:A8"/>
@@ -3702,18 +3830,22 @@
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F33:F34"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="E27:E28"/>
+    <mergeCell ref="D33:D34"/>
     <mergeCell ref="F27:F28"/>
+    <mergeCell ref="A33:A34"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B33:B34"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
@@ -3734,7 +3866,7 @@
     <mergeCell ref="C5:C6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3:O34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,N/A,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
